--- a/data/trans_camb/P2C_R1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,72</t>
+          <t>-1,47; 3,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,2</t>
+          <t>-3,07; 1,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 53,94</t>
+          <t>18,69; 56,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,23</t>
+          <t>2,25; 9,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,06</t>
+          <t>0,47; 4,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,33; 46,96</t>
+          <t>23,13; 49,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,5</t>
+          <t>1,19; 5,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,8</t>
+          <t>-0,85; 1,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 45,11</t>
+          <t>23,41; 45,63</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>498,01; —</t>
+          <t>565,8; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; —</t>
+          <t>26,6; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1208,25; —</t>
+          <t>1396,37; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,9; 35,77</t>
+          <t>14,15; 37,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,6</t>
+          <t>-2,95; 0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,86</t>
+          <t>-2,95; 0,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 20,08</t>
+          <t>8,77; 19,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,58</t>
+          <t>-1,43; 0,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,09</t>
+          <t>-1,09; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,94; 23,76</t>
+          <t>13,08; 23,89</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 235,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>314,74; 4466,35</t>
+          <t>270,85; 4023,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 301,56</t>
+          <t>-100,0; 283,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-96,75; 478,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>779,04; 7019,48</t>
+          <t>814,6; 11253,9</t>
         </is>
       </c>
     </row>
@@ -1114,42 +1114,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 44,1</t>
+          <t>19,31; 44,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,3</t>
+          <t>-1,77; 2,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,75</t>
+          <t>-1,94; 1,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,53; 41,93</t>
+          <t>24,24; 42,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,24</t>
+          <t>-0,81; 1,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,23</t>
+          <t>-0,85; 1,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 39,83</t>
+          <t>24,9; 40,49</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>925,55; —</t>
+          <t>873,82; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1641,95; —</t>
+          <t>1740,14; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,0</t>
+          <t>-2,31; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,49; 41,51</t>
+          <t>13,94; 40,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,71</t>
+          <t>0,63; 3,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,23</t>
+          <t>0,35; 3,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,34; 25,59</t>
+          <t>13,25; 26,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,66</t>
+          <t>-0,09; 1,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,42</t>
+          <t>-0,47; 1,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,29; 29,09</t>
+          <t>15,41; 29,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 2,91</t>
+          <t>-6,37; 3,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,5</t>
+          <t>-4,8; 4,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,74; 26,47</t>
+          <t>2,81; 26,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,0</t>
+          <t>-5,68; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 0,0</t>
+          <t>-5,1; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,19; 31,49</t>
+          <t>13,73; 33,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,07</t>
+          <t>-4,02; 1,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,73</t>
+          <t>-3,58; 1,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,21; 26,81</t>
+          <t>11,87; 26,4</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 784,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 2971,14</t>
+          <t>-27,18; 3189,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>293,89; —</t>
+          <t>297,36; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 286,79</t>
+          <t>-100,0; 317,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-88,54; 242,33</t>
+          <t>-97,55; 275,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>223,91; 2531,59</t>
+          <t>262,77; 2919,87</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,08</t>
+          <t>0,5; 4,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14,53; 31,8</t>
+          <t>14,51; 32,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,0</t>
+          <t>-4,6; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,63</t>
+          <t>-2,56; 2,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,2; 31,84</t>
+          <t>17,68; 31,61</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,75</t>
+          <t>-1,5; 0,77</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,26</t>
+          <t>-0,77; 2,28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18,03; 29,42</t>
+          <t>18,51; 29,78</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>385,63; —</t>
+          <t>494,62; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>891,43; —</t>
+          <t>908,5; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,01</t>
+          <t>0,03; 2,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,92</t>
+          <t>-0,24; 1,95</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,11; 21,09</t>
+          <t>4,16; 19,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,52</t>
+          <t>0,23; 2,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,48</t>
+          <t>-0,23; 1,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,39; 21,21</t>
+          <t>0,13; 21,56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,26</t>
+          <t>0,37; 2,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,31</t>
+          <t>-0,1; 1,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,62; 17,12</t>
+          <t>0,84; 17,46</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,87; —</t>
+          <t>-19,7; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-70,43; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>181,51; —</t>
+          <t>146,81; 16716,93</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,36</t>
+          <t>-2,39; 0,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,13</t>
+          <t>-1,49; 1,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,36</t>
+          <t>0,69; 5,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,34</t>
+          <t>-1,9; 0,27</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,04</t>
+          <t>-1,0; 1,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,89; 10,23</t>
+          <t>4,79; 10,31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,12</t>
+          <t>-1,45; 0,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,18</t>
+          <t>-0,89; 1,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,77</t>
+          <t>3,76; 7,56</t>
         </is>
       </c>
     </row>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 536,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 1814,71</t>
+          <t>-19,69; 2419,48</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2315,27 +2315,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-64,73; 732,03</t>
+          <t>-73,67; 513,16</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>260,09; 3749,76</t>
+          <t>206,03; 3153,11</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-91,72; 69,04</t>
+          <t>-91,9; 90,06</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-55,69; 288,11</t>
+          <t>-62,2; 242,02</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>202,54; 1643,21</t>
+          <t>233,29; 1634,93</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,73</t>
+          <t>-0,3; 0,79</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,95</t>
+          <t>-0,21; 0,9</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,43</t>
+          <t>13,05; 19,76</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,95</t>
+          <t>-0,29; 0,96</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,84</t>
+          <t>-0,34; 0,8</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,65; 17,39</t>
+          <t>6,51; 17,38</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,68</t>
+          <t>-0,16; 0,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,68</t>
+          <t>-0,18; 0,66</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,94; 17,05</t>
+          <t>7,8; 17,09</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 206,99</t>
+          <t>-41,25; 237,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 292,54</t>
+          <t>-31,9; 262,82</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1334,07; 5507,74</t>
+          <t>1426,03; 5527,47</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 198,03</t>
+          <t>-29,81; 190,34</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 172,11</t>
+          <t>-34,69; 166,19</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>634,53; 2977,19</t>
+          <t>660,06; 2867,39</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 139,92</t>
+          <t>-18,2; 136,33</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 133,0</t>
+          <t>-20,02; 137,04</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1052,54; 3156,47</t>
+          <t>1063,87; 3273,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34,98</t>
+          <t>30,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,27</t>
+          <t>31,99</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34,56</t>
+          <t>31,51</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,69</t>
+          <t>-1,53; 3,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,19</t>
+          <t>-2,99; 1,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,69; 56,09</t>
+          <t>15,03; 50,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,4</t>
+          <t>2,28; 9,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,33</t>
+          <t>0,46; 3,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,13; 49,58</t>
+          <t>20,66; 43,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,6</t>
+          <t>1,11; 5,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,82</t>
+          <t>-0,79; 1,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,41; 45,63</t>
+          <t>22,04; 41,12</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2904,87%</t>
+          <t>2573,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6113,79%</t>
+          <t>5574,9%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>565,8; —</t>
+          <t>293,72; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,6; —</t>
+          <t>11,13; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1396,37; —</t>
+          <t>1302,38; —</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,41</t>
+          <t>22,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,23</t>
+          <t>13,79</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,83</t>
+          <t>17,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,15; 37,36</t>
+          <t>12,92; 34,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,59</t>
+          <t>-2,75; 0,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,84</t>
+          <t>-2,64; 0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 19,96</t>
+          <t>8,6; 19,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,49</t>
+          <t>-1,37; 0,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,11</t>
+          <t>-1,05; 1,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,08; 23,89</t>
+          <t>12,0; 23,54</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1034,28%</t>
+          <t>1001,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2341,57%</t>
+          <t>2250,32%</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 235,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>270,85; 4023,6</t>
+          <t>291,58; 4181,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-96,75; 478,95</t>
+          <t>-100,0; 699,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>814,6; 11253,9</t>
+          <t>722,43; 8025,39</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30,5</t>
+          <t>28,7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,52</t>
+          <t>32,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31,71</t>
+          <t>31,08</t>
         </is>
       </c>
     </row>
@@ -1114,42 +1114,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,31; 44,23</t>
+          <t>17,82; 41,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,15</t>
+          <t>-1,59; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,36</t>
+          <t>-1,9; 1,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,24; 42,55</t>
+          <t>23,43; 42,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,26</t>
+          <t>-0,98; 1,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,44</t>
+          <t>-0,8; 1,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,9; 40,49</t>
+          <t>24,44; 40,0</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3443,21%</t>
+          <t>3473,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6182,18%</t>
+          <t>6059,53%</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>873,82; —</t>
+          <t>916,3; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1740,14; —</t>
+          <t>1579,65; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,75</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,76</t>
+          <t>17,26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21,39</t>
+          <t>19,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-2,62; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,0</t>
+          <t>-2,62; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,94; 40,83</t>
+          <t>11,99; 38,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,63</t>
+          <t>0,64; 3,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,29</t>
+          <t>0,34; 3,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 26,26</t>
+          <t>11,67; 23,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,79</t>
+          <t>-0,11; 1,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,29</t>
+          <t>-0,29; 1,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,41; 29,82</t>
+          <t>14,64; 28,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4724,77%</t>
+          <t>4276,6%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9114,32%</t>
+          <t>8358,32%</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,89</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,2</t>
+          <t>21,03</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18,3</t>
+          <t>16,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 3,33</t>
+          <t>-6,16; 3,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 4,64</t>
+          <t>-5,48; 4,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 26,57</t>
+          <t>2,27; 23,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,0</t>
+          <t>-5,19; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,0</t>
+          <t>-4,93; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,73; 33,92</t>
+          <t>12,91; 30,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,03</t>
+          <t>-4,04; 0,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,75</t>
+          <t>-3,3; 1,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,87; 26,4</t>
+          <t>10,44; 24,51</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>413,39%</t>
+          <t>347,56%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1366,35%</t>
+          <t>1294,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>812,96%</t>
+          <t>738,83%</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 638,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 3189,61</t>
+          <t>-36,24; 2405,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>297,36; —</t>
+          <t>272,98; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 317,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-97,55; 275,3</t>
+          <t>-89,01; 206,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>262,77; 2919,87</t>
+          <t>220,84; 2288,64</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22,7</t>
+          <t>21,6</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,03</t>
+          <t>23,67</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23,48</t>
+          <t>22,77</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,99</t>
+          <t>0,5; 4,97</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14,51; 32,64</t>
+          <t>14,02; 30,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,0</t>
+          <t>-4,15; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,16</t>
+          <t>-3,11; 1,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,68; 31,61</t>
+          <t>17,69; 32,47</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,77</t>
+          <t>-1,46; 0,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,28</t>
+          <t>-0,95; 2,33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18,51; 29,78</t>
+          <t>18,15; 29,0</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1881,21%</t>
+          <t>1852,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3509,6%</t>
+          <t>3403,68%</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>494,62; —</t>
+          <t>386,1; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>908,5; —</t>
+          <t>717,35; —</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10,12</t>
+          <t>10,96</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>19,19</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>15,77</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,99</t>
+          <t>0,04; 3,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,95</t>
+          <t>-0,38; 1,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,16; 19,24</t>
+          <t>4,57; 21,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,6</t>
+          <t>0,05; 2,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,67</t>
+          <t>-0,23; 1,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 21,56</t>
+          <t>12,33; 29,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,23</t>
+          <t>0,38; 2,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,29</t>
+          <t>-0,12; 1,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,84; 17,46</t>
+          <t>10,6; 23,44</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4332,04%</t>
+          <t>4692,07%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1840,77%</t>
+          <t>8550,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2210,25%</t>
+          <t>6902,15%</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,7; —</t>
+          <t>13,05; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,01; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>146,81; 16716,93</t>
+          <t>1501,65; —</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>7,42</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>5,52</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,37</t>
+          <t>-2,03; 0,38</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,22</t>
+          <t>-1,57; 1,17</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,81</t>
+          <t>0,4; 5,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,27</t>
+          <t>-2,02; 0,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,87</t>
+          <t>-0,82; 1,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,31</t>
+          <t>4,87; 10,52</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,19</t>
+          <t>-1,38; 0,13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,16</t>
+          <t>-0,71; 1,29</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,56</t>
+          <t>3,74; 7,54</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>326,65%</t>
+          <t>307,11%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>798,63%</t>
+          <t>798,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>622,52%</t>
+          <t>612,42%</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 2419,48</t>
+          <t>-22,42; 2320,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2315,27 +2315,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-73,67; 513,16</t>
+          <t>-66,59; 554,34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>206,03; 3153,11</t>
+          <t>220,45; 3760,65</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-91,9; 90,06</t>
+          <t>-89,66; 67,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,2; 242,02</t>
+          <t>-50,53; 320,03</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>233,29; 1634,93</t>
+          <t>234,0; 1753,32</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>14,55</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,64</t>
+          <t>15,89</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,86</t>
+          <t>15,34</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,79</t>
+          <t>-0,38; 0,75</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,9</t>
+          <t>-0,25; 0,91</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13,05; 19,76</t>
+          <t>11,95; 18,25</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,96</t>
+          <t>-0,2; 1,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,8</t>
+          <t>-0,38; 0,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,51; 17,38</t>
+          <t>13,85; 17,92</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,68</t>
+          <t>-0,09; 0,71</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,66</t>
+          <t>-0,12; 0,67</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,8; 17,09</t>
+          <t>13,68; 17,29</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2772,29%</t>
+          <t>2513,39%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1641,36%</t>
+          <t>2063,17%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2028,51%</t>
+          <t>2244,72%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 237,38</t>
+          <t>-45,78; 232,45</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 262,82</t>
+          <t>-38,34; 311,74</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1426,03; 5527,47</t>
+          <t>1172,66; 5418,95</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 190,34</t>
+          <t>-25,37; 211,14</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 166,19</t>
+          <t>-35,7; 150,17</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>660,06; 2867,39</t>
+          <t>1197,08; 3695,86</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 136,33</t>
+          <t>-10,37; 148,54</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 137,04</t>
+          <t>-14,8; 143,62</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1063,87; 3273,38</t>
+          <t>1480,24; 3585,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R1-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R1-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
